--- a/HDMITool/demo/屏幕设备上位机和工具通讯协议.xlsx
+++ b/HDMITool/demo/屏幕设备上位机和工具通讯协议.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">上位机客户端本地主机地址127.0.0.1本地主机端口7920   </t>
     </r>
     <r>
@@ -59,6 +66,18 @@
     <t>上位机接收</t>
   </si>
   <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>上电</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -105,6 +124,28 @@
   </si>
   <si>
     <t>第四个画面推完</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>读取电流（10次间隔500ms，去最大最小值后取平均值）</t>
+  </si>
+  <si>
+    <t>B5=val
+示例(单位A)：B5=0.0005</t>
+  </si>
+  <si>
+    <t>返回电流值</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>下电</t>
+  </si>
+  <si>
+    <t>B6</t>
   </si>
 </sst>
 </file>
@@ -756,17 +797,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1293,8 +1334,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="23.375" customWidth="1"/>
@@ -1308,116 +1349,169 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:6">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="27" customHeight="1" spans="1:6">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="29" customHeight="1" spans="1:6">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+    <row r="7" ht="27" customHeight="1" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="47" customHeight="1" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
